--- a/Lewitus_etal_2014/pbio.1002000.s014.xlsx
+++ b/Lewitus_etal_2014/pbio.1002000.s014.xlsx
@@ -2569,8 +2569,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -2843,7 +2843,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBB309A1-871F-41AF-BE73-9DA3DFA94164}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF39DC8A-A157-423F-8222-DE24A36867EF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
